--- a/backend/data/financials_by_company/1AD.AX.xlsx
+++ b/backend/data/financials_by_company/1AD.AX.xlsx
@@ -3494,10 +3494,8 @@
           <t>VIC</t>
         </is>
       </c>
-      <c r="E2" t="inlineStr">
-        <is>
-          <t>3124</t>
-        </is>
+      <c r="E2" t="n">
+        <v>3124</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
@@ -3699,7 +3697,7 @@
         <v>2549669043</v>
       </c>
       <c r="BK2" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="BL2" t="n">
         <v>1751241600</v>
@@ -3714,7 +3712,7 @@
         <v>-4362978</v>
       </c>
       <c r="BP2" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="BQ2" t="n">
         <v>-0.03</v>
@@ -3936,7 +3934,7 @@
         <v>1</v>
       </c>
       <c r="DX2" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="DY2" t="n">
         <v>-0.03</v>
